--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>864714</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>815400</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>808870</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>798166</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>765768.5</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>724575.5</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>712500</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>710770</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>706610</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>674350</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>659980</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>637750</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>631625</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>627819</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -577,9 +530,6 @@
       </c>
       <c r="B16">
         <v>601521</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>864714</v>
       </c>
+      <c r="C2">
+        <v>754690</v>
+      </c>
+      <c r="D2">
+        <v>110024</v>
+      </c>
+      <c r="E2">
+        <v>14.5787011885675</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>815400</v>
       </c>
+      <c r="C3">
+        <v>700000</v>
+      </c>
+      <c r="D3">
+        <v>115400</v>
+      </c>
+      <c r="E3">
+        <v>16.48571428571428</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>808870</v>
       </c>
+      <c r="C4">
+        <v>719168</v>
+      </c>
+      <c r="D4">
+        <v>89702</v>
+      </c>
+      <c r="E4">
+        <v>12.47302438373232</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>798166</v>
       </c>
+      <c r="C5">
+        <v>705740</v>
+      </c>
+      <c r="D5">
+        <v>92426</v>
+      </c>
+      <c r="E5">
+        <v>13.09632442542579</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,105 +467,204 @@
       <c r="B6">
         <v>765768.5</v>
       </c>
+      <c r="C6">
+        <v>674433</v>
+      </c>
+      <c r="D6">
+        <v>91335.5</v>
+      </c>
+      <c r="E6">
+        <v>13.54256093637174</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7">
-        <v>724575.5</v>
+        <v>758542</v>
+      </c>
+      <c r="C7">
+        <v>663788</v>
+      </c>
+      <c r="D7">
+        <v>94754</v>
+      </c>
+      <c r="E7">
+        <v>14.27473832006605</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B8">
-        <v>712500</v>
+        <v>724575.5</v>
+      </c>
+      <c r="C8">
+        <v>606912</v>
+      </c>
+      <c r="D8">
+        <v>117663.5</v>
+      </c>
+      <c r="E8">
+        <v>19.38724230201414</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="B9">
-        <v>710770</v>
+        <v>712500</v>
+      </c>
+      <c r="C9">
+        <v>613045</v>
+      </c>
+      <c r="D9">
+        <v>99455</v>
+      </c>
+      <c r="E9">
+        <v>16.2231157582233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B10">
-        <v>706610</v>
+        <v>710770</v>
+      </c>
+      <c r="C10">
+        <v>594826</v>
+      </c>
+      <c r="D10">
+        <v>115944</v>
+      </c>
+      <c r="E10">
+        <v>19.49208676150673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="B11">
-        <v>674350</v>
+        <v>706610</v>
+      </c>
+      <c r="C11">
+        <v>640418</v>
+      </c>
+      <c r="D11">
+        <v>66192</v>
+      </c>
+      <c r="E11">
+        <v>10.33574946363156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="B12">
-        <v>659980</v>
+        <v>674350</v>
+      </c>
+      <c r="C12">
+        <v>555591</v>
+      </c>
+      <c r="D12">
+        <v>118759</v>
+      </c>
+      <c r="E12">
+        <v>21.37525625865069</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="B13">
-        <v>637750</v>
+        <v>659980</v>
+      </c>
+      <c r="C13">
+        <v>582490</v>
+      </c>
+      <c r="D13">
+        <v>77490</v>
+      </c>
+      <c r="E13">
+        <v>13.30323267352229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="B14">
-        <v>631625</v>
+        <v>637750</v>
+      </c>
+      <c r="C14">
+        <v>593179</v>
+      </c>
+      <c r="D14">
+        <v>44571</v>
+      </c>
+      <c r="E14">
+        <v>7.513920755792092</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B15">
-        <v>627819</v>
+        <v>631625</v>
+      </c>
+      <c r="C15">
+        <v>558058</v>
+      </c>
+      <c r="D15">
+        <v>73567</v>
+      </c>
+      <c r="E15">
+        <v>13.18267993649405</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="B16">
-        <v>601521</v>
+        <v>627819</v>
+      </c>
+      <c r="C16">
+        <v>550309.5</v>
+      </c>
+      <c r="D16">
+        <v>77509.5</v>
+      </c>
+      <c r="E16">
+        <v>14.08471051290228</v>
       </c>
     </row>
   </sheetData>
@@ -539,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -657,50 +792,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B12">
-        <v>601521</v>
+        <v>724575.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B13">
-        <v>724575.5</v>
+        <v>710770</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="B14">
-        <v>710770</v>
+        <v>808870</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B15">
-        <v>808870</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vicuña</t>
-        </is>
-      </c>
-      <c r="B16">
         <v>631625</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -683,11 +683,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -695,138 +690,103 @@
           <t>Andacollo</t>
         </is>
       </c>
-      <c r="B2">
-        <v>815400</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canela</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>712500</v>
+          <t>Los Vilos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>674350</v>
+          <t>Canela</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>765768.5</v>
+          <t>Ovalle</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Illapel</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>798166</v>
+          <t>Coquimbo</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>La Higuera</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>637750</v>
+          <t>La Serena</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>864714</v>
+          <t>Combarbalá</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>706610</v>
+          <t>Punitaqui</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>627819</v>
+          <t>Paihuano</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovalle</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>659980</v>
+          <t>Illapel</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>724575.5</v>
+          <t>La Higuera</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>710770</v>
+          <t>Monte Patria</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salamanca</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>808870</v>
+          <t>Río Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Vicuña</t>
         </is>
-      </c>
-      <c r="B15">
-        <v>631625</v>
       </c>
     </row>
   </sheetData>
